--- a/eds-block-mapping-report.xlsx
+++ b/eds-block-mapping-report.xlsx
@@ -400,15 +400,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I16"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
-    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" customWidth="1"/>
+    <col min="4" max="4" width="65.83203125" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="35.83203125" customWidth="1"/>
-    <col min="9" max="9" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="42.83203125" customWidth="1"/>
+    <col min="9" max="9" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -418,82 +418,58 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>Scope: Homepage + Inspect Page + Header/Footer</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
         <v>Generated: 2026-05-04</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Block Name</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Category</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Page(s)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Description</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Original Component</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Complexity</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Variants</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Development Notes</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>header</v>
+        <v>Block Name</v>
       </c>
       <c r="B5" t="str">
-        <v>Navigation</v>
+        <v>Category</v>
       </c>
       <c r="C5" t="str">
-        <v>All Pages</v>
+        <v>Page(s)</v>
       </c>
       <c r="D5" t="str">
-        <v>Top navigation bar with brand logo (Content Authenticity + Beta badge), nav links (Home, Inspect), CTA button (Add Chrome extension), app switcher grid icon, and Sign in button.</v>
+        <v>Description</v>
       </c>
       <c r="E5" t="str">
-        <v>Fixed top nav bar with responsive hamburger menu</v>
+        <v>Original Component</v>
       </c>
       <c r="F5" t="str">
-        <v>P0 - Critical</v>
+        <v>Priority</v>
       </c>
       <c r="G5" t="str">
-        <v>Medium</v>
+        <v>Complexity</v>
       </c>
       <c r="H5" t="str">
-        <v>Desktop (full nav), Mobile (hamburger + slide-out panel)</v>
+        <v>Variants</v>
       </c>
       <c r="I5" t="str">
-        <v>Uses Adobe Universal Nav for app switcher and profile. Sticky/fixed position.</v>
+        <v>Development Notes</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>hero</v>
+        <v>header</v>
       </c>
       <c r="B6" t="str">
-        <v>Hero</v>
+        <v>Navigation</v>
       </c>
       <c r="C6" t="str">
-        <v>Homepage</v>
+        <v>All Pages</v>
       </c>
       <c r="D6" t="str">
-        <v>Full-width hero section with gradient purple-to-coral background, large heading "Sign your work with Content Credentials", descriptive paragraph, CTA button "Get started", and a decorative illustration image on the right.</v>
+        <v>Top navigation bar with: brand logo (Content Authenticity + Beta badge), nav links (Preferences, Apply, Manage, Inspect, Help), CTA button (Join Discord), icon button, app switcher grid, and profile/Sign in.</v>
       </c>
       <c r="E6" t="str">
-        <v>Hero section with gradient background + illustration</v>
+        <v>Fixed top nav bar with responsive hamburger</v>
       </c>
       <c r="F6" t="str">
         <v>P0 - Critical</v>
@@ -502,73 +478,73 @@
         <v>Medium</v>
       </c>
       <c r="H6" t="str">
-        <v>Homepage hero (gradient bg + image)</v>
+        <v>Desktop (full nav links), Mobile (hamburger + slide-out)</v>
       </c>
       <c r="I6" t="str">
-        <v>Gradient background: purple → coral. Illustration is a colorful artistic image. Responsive: image below text on mobile.</v>
+        <v>Nav links: Preferences, Apply, Manage, Inspect, Help. CTA: "Join Discord". Uses Adobe Universal Nav for app switcher + profile. Sticky positioned.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>cards</v>
+        <v>footer</v>
       </c>
       <c r="B7" t="str">
-        <v>Content</v>
+        <v>Navigation</v>
       </c>
       <c r="C7" t="str">
-        <v>Homepage</v>
+        <v>All Pages</v>
       </c>
       <c r="D7" t="str">
-        <v>3-column card grid with icons, headings, descriptions, and CTA links. Cards: "Sign your work" (lock icon), "Ask AI not to use your content" (shield icon), "Inspect Content Credentials" (magnifier icon).</v>
+        <v>Minimal footer with Adobe branding, legal links, and copyright notice.</v>
       </c>
       <c r="E7" t="str">
-        <v>3-up feature cards with icons and CTAs</v>
+        <v>Minimal site footer</v>
       </c>
       <c r="F7" t="str">
-        <v>P0 - Critical</v>
+        <v>P1 - High</v>
       </c>
       <c r="G7" t="str">
         <v>Low</v>
       </c>
       <c r="H7" t="str">
-        <v>Icon cards (3-up grid)</v>
+        <v>Minimal (links + copyright)</v>
       </c>
       <c r="I7" t="str">
-        <v>Each card has: icon image, heading, body text, and "Learn more" style link. Light background.</v>
+        <v>Lightweight footer following Adobe standard pattern.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>columns</v>
+        <v>hero</v>
       </c>
       <c r="B8" t="str">
-        <v>Content</v>
+        <v>Hero</v>
       </c>
       <c r="C8" t="str">
         <v>Homepage</v>
       </c>
       <c r="D8" t="str">
-        <v>2-column layout: left column has rich text content (What are Content Credentials, How to apply, Your Content Credentials are durable, Where yours work) with bold headings and body text. Right column has a decorative illustration showing Content Credentials UI.</v>
+        <v>Full-width hero with gradient purple-to-coral background. Large heading "Sign your work with Content Credentials", descriptive paragraph, "Get started" CTA button, and decorative illustration image on right.</v>
       </c>
       <c r="E8" t="str">
-        <v>2-column text + image layout</v>
+        <v>Hero with gradient background + illustration</v>
       </c>
       <c r="F8" t="str">
-        <v>P1 - High</v>
+        <v>P0 - Critical</v>
       </c>
       <c r="G8" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="H8" t="str">
-        <v>Text-left + Image-right</v>
+        <v>Gradient background with right-side image</v>
       </c>
       <c r="I8" t="str">
-        <v>Section heading "Protect your work before sharing it online" sits above the columns. Content has multiple sub-headings with paragraphs.</v>
+        <v>CSS gradient: purple → pink → coral. Illustration is decorative artwork. Image stacks below text on mobile.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>accordion</v>
+        <v>cards</v>
       </c>
       <c r="B9" t="str">
         <v>Content</v>
@@ -577,10 +553,10 @@
         <v>Homepage</v>
       </c>
       <c r="D9" t="str">
-        <v>FAQ section with heading "Still have questions?" followed by expandable Q&amp;A items. Questions include: "Is Adobe Content Authenticity Beta free?", "What is Content Credentials?", "How are Content Credentials unique?", etc.</v>
+        <v>3-column card grid. Each card has: icon, heading, description, CTA link. Cards: "Sign your work" (lock icon), "Ask AI not to use your content" (shield icon), "Inspect Content Credentials" (magnifier icon).</v>
       </c>
       <c r="E9" t="str">
-        <v>FAQ accordion with 7+ questions</v>
+        <v>3-up feature cards with icons and CTAs</v>
       </c>
       <c r="F9" t="str">
         <v>P1 - High</v>
@@ -589,213 +565,213 @@
         <v>Low</v>
       </c>
       <c r="H9" t="str">
-        <v>FAQ variant (multi-open)</v>
+        <v>3-up icon cards</v>
       </c>
       <c r="I9" t="str">
-        <v>2-column layout: left has section title, right has the accordion items. Clean minimal styling.</v>
+        <v>Each card: icon image + heading + body text + "Learn more" link. White card on light background.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>file-upload</v>
+        <v>columns</v>
       </c>
       <c r="B10" t="str">
-        <v>Interactive</v>
+        <v>Content</v>
       </c>
       <c r="C10" t="str">
-        <v>Inspect Page</v>
+        <v>Homepage</v>
       </c>
       <c r="D10" t="str">
-        <v>Drag-and-drop file upload area with dashed border, gradient icon (image + checkmark), heading "Drag and drop your file", subtext "Select a file from your device", and "Browse files" button.</v>
+        <v>2-column layout. Left: rich text with multiple sub-sections (What are Content Credentials, How to apply, Durability, Where they work). Right: decorative Content Credentials UI illustration.</v>
       </c>
       <c r="E10" t="str">
-        <v>File upload dropzone with drag-and-drop</v>
+        <v>2-column text + image information section</v>
       </c>
       <c r="F10" t="str">
-        <v>P0 - Critical</v>
+        <v>P1 - High</v>
       </c>
       <c r="G10" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="H10" t="str">
-        <v>Default (empty state), Active (file dragged over)</v>
+        <v>Text-left + Image-right</v>
       </c>
       <c r="I10" t="str">
-        <v>Custom block - not standard EDS. Requires JavaScript for drag-and-drop, file reading, and C2PA credential inspection. Core app functionality.</v>
+        <v>Section heading "Protect your work before sharing it online" above columns. Left column has bold subheadings with body text.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>inspect-info</v>
+        <v>accordion</v>
       </c>
       <c r="B11" t="str">
         <v>Content</v>
       </c>
       <c r="C11" t="str">
-        <v>Inspect Page</v>
+        <v>Homepage</v>
       </c>
       <c r="D11" t="str">
-        <v>Left sidebar panel with page heading "Inspect", description text about Content Credentials inspection, and supported formats list (AVI, AVIF, C2PA, DNG, GIF, HEIC, HEIF, JPEG, M4A, MOV, MP3, MP4, PDF, PNG, SVG, TIFF, WAV, WebP).</v>
+        <v>FAQ section with heading "Still have questions?" and expandable Q&amp;A items. Questions: "Is it free?", "What is Content Credentials?", "How unique?", "What happens when I apply?", "How can it protect my content?", etc.</v>
       </c>
       <c r="E11" t="str">
-        <v>Inspect page intro/sidebar content</v>
+        <v>FAQ accordion (~7 questions)</v>
       </c>
       <c r="F11" t="str">
-        <v>P0 - Critical</v>
+        <v>P1 - High</v>
       </c>
       <c r="G11" t="str">
         <v>Low</v>
       </c>
       <c r="H11" t="str">
-        <v>Default content (heading + description + format list)</v>
+        <v>FAQ multi-open, 2-column layout (title left, items right)</v>
       </c>
       <c r="I11" t="str">
-        <v>Can be modeled as default content (no block needed) - just text in the section with appropriate styling.</v>
+        <v>Left side: section title. Right side: accordion items. Clean minimal styling, border-bottom separators.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>footer</v>
+        <v>file-upload</v>
       </c>
       <c r="B12" t="str">
-        <v>Navigation</v>
+        <v>Interactive</v>
       </c>
       <c r="C12" t="str">
-        <v>All Pages</v>
+        <v>Inspect Page (empty state)</v>
       </c>
       <c r="D12" t="str">
-        <v>Minimal footer with Adobe branding, legal links, copyright notice.</v>
+        <v>Two-panel layout for the upload state. Left panel: "Inspect" heading, description text, supported formats list. Right panel: large drag-and-drop zone with dashed border, gradient icon, "Drag and drop your file" heading, "Select a file from your device" text, "Browse files" button.</v>
       </c>
       <c r="E12" t="str">
-        <v>Minimal site footer</v>
+        <v>File upload dropzone with info sidebar</v>
       </c>
       <c r="F12" t="str">
-        <v>P1 - High</v>
+        <v>P0 - Critical</v>
       </c>
       <c r="G12" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="H12" t="str">
-        <v>Minimal (links + copyright)</v>
+        <v>Empty state, Drag-over highlight state, Processing/loading state</v>
       </c>
       <c r="I12" t="str">
-        <v>Very lightweight footer. May use Adobe standard footer pattern.</v>
+        <v>Custom block with JS for drag-and-drop, file validation (AVI, AVIF, C2PA, DNG, GIF, HEIC, HEIF, JPEG, M4A, MOV, MP3, MP4, PDF, PNG, SVG, TIFF, WAV, WebP), and C2PA SDK integration.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>section (gradient-bg)</v>
+        <v>credentials-panel</v>
       </c>
       <c r="B13" t="str">
-        <v>Section Styling</v>
+        <v>Interactive</v>
       </c>
       <c r="C13" t="str">
-        <v>Homepage</v>
+        <v>Inspect Page (results state)</v>
       </c>
       <c r="D13" t="str">
-        <v>Section with purple-to-coral gradient background used for the hero area.</v>
+        <v>Left sidebar showing: "Content Credentials" heading, file thumbnail with filename + recorder name (e.g. "h3-kafd-riyadh.jpg / Recorded by Adobe Inc."), "Retrieved from the selected content" note with info icon, "Search for possible matches" action link with icon, "Inspect another file or drag and drop anywhere" action link with icon.</v>
       </c>
       <c r="E13" t="str">
-        <v>Gradient background section wrapper</v>
+        <v>Content Credentials left panel with file info and actions</v>
       </c>
       <c r="F13" t="str">
-        <v>P1 - High</v>
+        <v>P0 - Critical</v>
       </c>
       <c r="G13" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="H13" t="str">
-        <v>Gradient purple-coral</v>
+        <v>Single credential, Multiple credentials (list)</v>
       </c>
       <c r="I13" t="str">
-        <v>Implemented as section metadata style class, not a separate block. CSS gradient: purple → pink → coral.</v>
+        <v>Dynamically populated after file upload. Shows thumbnail preview, metadata from C2PA manifest. Action links trigger new workflows.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>section (gray-bg)</v>
+        <v>image-viewer</v>
       </c>
       <c r="B14" t="str">
-        <v>Section Styling</v>
+        <v>Interactive</v>
       </c>
       <c r="C14" t="str">
-        <v>Homepage, Inspect</v>
+        <v>Inspect Page (results state)</v>
       </c>
       <c r="D14" t="str">
-        <v>Section with light gray (#f5f5f5) background used for content areas.</v>
+        <v>Center panel with credential chain visualization. Shows connected image nodes in a vertical tree/flow (parent → child). Each node shows the image with a CR badge or warning icon. Includes zoom controls (+, Fit, -) and a "Compare" button.</v>
       </c>
       <c r="E14" t="str">
-        <v>Light gray section wrapper</v>
+        <v>Credential chain viewer with zoom and compare</v>
       </c>
       <c r="F14" t="str">
-        <v>P2 - Medium</v>
+        <v>P0 - Critical</v>
       </c>
       <c r="G14" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="H14" t="str">
-        <v>Light gray background</v>
+        <v>Single node, Multi-node chain, Compare view</v>
       </c>
       <c r="I14" t="str">
-        <v>Implemented as section metadata style class.</v>
+        <v>Complex interactive component. Displays provenance chain (history of edits). Zoom controls for image inspection. Compare button for side-by-side original vs edited. Connected nodes with lines.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>button (default content)</v>
+        <v>details-panel</v>
       </c>
       <c r="B15" t="str">
-        <v>UI Element</v>
+        <v>Interactive</v>
       </c>
       <c r="C15" t="str">
-        <v>All Pages</v>
+        <v>Inspect Page (results state)</v>
       </c>
       <c r="D15" t="str">
-        <v>Primary action buttons used throughout the site: "Get started", "Learn more", "Browse files", "Add Chrome extension". Black filled with white text, rounded corners.</v>
+        <v>Right sidebar showing file details: filename + recorder at top, large image preview with expand icon, collapsible "Content details" section with: "App or device used" (e.g. Adobe Content Authenticity with icon), "Recorded by" (e.g. Adobe Inc. on May 4, 2026 with icon), "Actions" section listing what was done to the content.</v>
       </c>
       <c r="E15" t="str">
-        <v>Spectrum-style primary buttons</v>
+        <v>Content details right panel with metadata accordion</v>
       </c>
       <c r="F15" t="str">
         <v>P0 - Critical</v>
       </c>
       <c r="G15" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="H15" t="str">
-        <v>Primary (filled black), Secondary (outlined)</v>
+        <v>Default expanded, Collapsed sections</v>
       </c>
       <c r="I15" t="str">
-        <v>Standard EDS button decoration via link styling. No block needed - handled by default content button decoration in scripts.js.</v>
+        <v>Dynamically populated from C2PA manifest data. Accordion-style collapsible sections. Shows app icons, dates, signer info. "Actions" lists edits (crop, resize, filter, etc.).</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>toast</v>
+        <v>compare-view</v>
       </c>
       <c r="B16" t="str">
-        <v>UI Element</v>
+        <v>Interactive</v>
       </c>
       <c r="C16" t="str">
-        <v>All Pages</v>
+        <v>Inspect Page (compare mode)</v>
       </c>
       <c r="D16" t="str">
-        <v>Bottom-positioned notification messages for user feedback (file upload status, errors, etc.).</v>
+        <v>Side-by-side or overlay comparison view triggered by "Compare" button. Shows original vs edited versions of the image for visual diff.</v>
       </c>
       <c r="E16" t="str">
-        <v>Toast notification overlay</v>
+        <v>Image comparison slider/overlay</v>
       </c>
       <c r="F16" t="str">
         <v>P2 - Medium</v>
       </c>
       <c r="G16" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="H16" t="str">
-        <v>Success, Error, Info</v>
+        <v>Side-by-side, Overlay slider</v>
       </c>
       <c r="I16" t="str">
-        <v>Purely JavaScript-driven UI element. Not authored content - generated by application logic.</v>
+        <v>Triggered from image-viewer "Compare" button. May use slider-based before/after pattern or toggle.</v>
       </c>
     </row>
   </sheetData>
@@ -807,9 +783,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B45"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="100.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -828,10 +804,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Pages Analyzed</v>
+        <v>Pages in Scope</v>
       </c>
       <c r="B4" t="str">
-        <v>2 (Homepage + Inspect page)</v>
+        <v>Homepage, Inspect Page (empty + results state), Header, Footer</v>
       </c>
     </row>
     <row r="5">
@@ -839,12 +815,12 @@
         <v>Total Blocks Identified</v>
       </c>
       <c r="B5" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Framework</v>
+        <v>Current Framework</v>
       </c>
       <c r="B6" t="str">
         <v>SvelteKit + Adobe Spectrum Design System (Tailwind CSS)</v>
@@ -876,7 +852,7 @@
         <v>P2 - Medium</v>
       </c>
       <c r="B11" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -889,7 +865,7 @@
         <v>Low</v>
       </c>
       <c r="B14" t="str">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -905,72 +881,171 @@
         <v>High</v>
       </c>
       <c r="B16" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Key Observations</v>
+        <v>Page: Homepage - Blocks</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>1. The site is currently built with SvelteKit (client-side JS app). Migration to EDS requires converting from SPA to document-based authoring.</v>
+        <v>hero</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Gradient hero with illustration</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2. The Inspect page has a complex interactive file-upload + C2PA inspection tool that will require custom JavaScript development.</v>
+        <v>cards</v>
+      </c>
+      <c r="B20" t="str">
+        <v>3-up feature cards with icons</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>3. The design uses Adobe Spectrum design system tokens (colors, typography, spacing) which should be mapped to EDS CSS custom properties.</v>
+        <v>columns</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2-col text + image (Protect your work)</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>4. Navigation uses Adobe Universal Nav component for app switcher and profile - this may need a custom integration or simplified version.</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>5. Most content sections (hero, cards, FAQ, columns) map cleanly to standard EDS blocks.</v>
+        <v>accordion</v>
+      </c>
+      <c r="B22" t="str">
+        <v>FAQ section with expandable Q&amp;A</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>6. The gradient backgrounds and illustration images are decorative and can be handled with section metadata styling.</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Recommended Development Order</v>
+        <v>Page: Inspect (Empty State) - Blocks</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>file-upload</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Info sidebar + drag-and-drop upload zone</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Phase 1: Core structure - header, footer, global styles, design tokens</v>
+        <v>Page: Inspect (Results State) - Blocks</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Phase 2: Homepage content blocks - hero, cards, columns, accordion (FAQ)</v>
+        <v>credentials-panel</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Left: file info, thumbnail, action links</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Phase 3: Interactive functionality - file-upload block, inspect results display</v>
+        <v>image-viewer</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Center: credential chain tree, zoom, compare button</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Phase 4: Polish - animations, responsive refinements, accessibility</v>
+        <v>details-panel</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Right: metadata, app info, recorder, actions accordion</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>compare-view</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Triggered overlay/side-by-side comparison</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Recommended Development Phases</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Phase 1 (Foundation)</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Header, Footer, global styles/tokens, design system setup</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Phase 2 (Homepage)</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Hero, Cards, Columns, Accordion blocks</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Phase 3 (Inspect Core)</v>
+      </c>
+      <c r="B36" t="str">
+        <v>File-upload block with drag-and-drop + C2PA SDK integration</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Phase 4 (Inspect Results)</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Credentials-panel, Image-viewer, Details-panel, Compare-view</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Key Technical Notes</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>1. C2PA SDK integration required for reading Content Credentials from uploaded files.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2. Inspect results state is entirely JS-driven — blocks render dynamically based on parsed file data.</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>3. Image-viewer requires canvas/SVG for the credential chain tree visualization with connecting lines.</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>4. Details-panel uses accordion sub-sections populated from C2PA manifest (signer, actions, assertions).</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>5. Homepage blocks are standard EDS content blocks — straightforward to implement.</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>6. Header nav includes: Preferences, Apply, Manage, Inspect, Help + "Join Discord" CTA.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/eds-block-mapping-report.xlsx
+++ b/eds-block-mapping-report.xlsx
@@ -398,32 +398,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I12"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" customWidth="1"/>
-    <col min="4" max="4" width="65.83203125" customWidth="1"/>
-    <col min="5" max="5" width="45.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="70.83203125" customWidth="1"/>
+    <col min="5" max="5" width="48.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="42.83203125" customWidth="1"/>
-    <col min="9" max="9" width="60.83203125" customWidth="1"/>
+    <col min="8" max="8" width="45.83203125" customWidth="1"/>
+    <col min="9" max="9" width="65.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>EDS Block Mapping Report - contentauthenticity.adobe.com</v>
+        <v>EDS Block Mapping Report - contentauthenticity.adobe.com/inspect</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Scope: Homepage + Inspect Page + Header/Footer</v>
+        <v>Scope: Inspect Page (empty + results state) + Header + Footer</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Generated: 2026-05-04</v>
+        <v>Generated: 2026-05-05</v>
       </c>
     </row>
     <row r="5">
@@ -515,275 +515,159 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>hero</v>
+        <v>file-upload</v>
       </c>
       <c r="B8" t="str">
-        <v>Hero</v>
+        <v>Interactive</v>
       </c>
       <c r="C8" t="str">
-        <v>Homepage</v>
+        <v>Inspect Page (empty state)</v>
       </c>
       <c r="D8" t="str">
-        <v>Full-width hero with gradient purple-to-coral background. Large heading "Sign your work with Content Credentials", descriptive paragraph, "Get started" CTA button, and decorative illustration image on right.</v>
+        <v>Two-panel layout for the upload state. Left panel: "Inspect" heading, description text, supported formats list (AVI, AVIF, C2PA, DNG, GIF, HEIC, HEIF, JPEG, M4A, MOV, MP3, MP4, PDF, PNG, SVG, TIFF, WAV, WebP). Right panel: large drag-and-drop zone with rounded dashed border, gradient icon (image + checkmark), "Drag and drop your file" heading, "Select a file from your device" text, "Browse files" button.</v>
       </c>
       <c r="E8" t="str">
-        <v>Hero with gradient background + illustration</v>
+        <v>File upload dropzone with info sidebar</v>
       </c>
       <c r="F8" t="str">
         <v>P0 - Critical</v>
       </c>
       <c r="G8" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="H8" t="str">
-        <v>Gradient background with right-side image</v>
+        <v>Empty state, Drag-over highlight state, Processing/loading state</v>
       </c>
       <c r="I8" t="str">
-        <v>CSS gradient: purple → pink → coral. Illustration is decorative artwork. Image stacks below text on mobile.</v>
+        <v>Custom block with JS for drag-and-drop, file validation, and C2PA SDK integration. Supported formats list displayed in left panel.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>cards</v>
+        <v>credentials-panel</v>
       </c>
       <c r="B9" t="str">
-        <v>Content</v>
+        <v>Interactive</v>
       </c>
       <c r="C9" t="str">
-        <v>Homepage</v>
+        <v>Inspect Page (results state - left)</v>
       </c>
       <c r="D9" t="str">
-        <v>3-column card grid. Each card has: icon, heading, description, CTA link. Cards: "Sign your work" (lock icon), "Ask AI not to use your content" (shield icon), "Inspect Content Credentials" (magnifier icon).</v>
+        <v>Left sidebar showing: "Content Credentials" heading, file thumbnail with filename + recorder name (e.g. "h3-kafd-riyadh.jpg / Recorded by Adobe Inc."), "Retrieved from the selected content" note with info icon, "Search for possible matches" action link with search icon, "Inspect another file or drag and drop anywhere" action link with upload icon.</v>
       </c>
       <c r="E9" t="str">
-        <v>3-up feature cards with icons and CTAs</v>
+        <v>Content Credentials left panel with file info and actions</v>
       </c>
       <c r="F9" t="str">
-        <v>P1 - High</v>
+        <v>P0 - Critical</v>
       </c>
       <c r="G9" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="H9" t="str">
-        <v>3-up icon cards</v>
+        <v>Single credential, Multiple credentials (list)</v>
       </c>
       <c r="I9" t="str">
-        <v>Each card: icon image + heading + body text + "Learn more" link. White card on light background.</v>
+        <v>Dynamically populated after file upload. Shows thumbnail preview, metadata from C2PA manifest. Action links trigger new workflows. Fixed-width sidebar.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>columns</v>
+        <v>image-viewer</v>
       </c>
       <c r="B10" t="str">
-        <v>Content</v>
+        <v>Interactive</v>
       </c>
       <c r="C10" t="str">
-        <v>Homepage</v>
+        <v>Inspect Page (results state - center)</v>
       </c>
       <c r="D10" t="str">
-        <v>2-column layout. Left: rich text with multiple sub-sections (What are Content Credentials, How to apply, Durability, Where they work). Right: decorative Content Credentials UI illustration.</v>
+        <v>Center panel with credential chain visualization. Shows connected image nodes in a vertical tree/flow (parent → child with connecting lines). Each node shows the image with a CR badge (valid) or warning triangle icon (issue). Includes zoom controls (+, Fit, -) and a "Compare" button at bottom.</v>
       </c>
       <c r="E10" t="str">
-        <v>2-column text + image information section</v>
+        <v>Credential chain viewer with zoom and compare</v>
       </c>
       <c r="F10" t="str">
-        <v>P1 - High</v>
+        <v>P0 - Critical</v>
       </c>
       <c r="G10" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="H10" t="str">
-        <v>Text-left + Image-right</v>
+        <v>Single node, Multi-node chain (vertical tree), Compare mode</v>
       </c>
       <c r="I10" t="str">
-        <v>Section heading "Protect your work before sharing it online" above columns. Left column has bold subheadings with body text.</v>
+        <v>Complex interactive component. Displays provenance chain (history of edits). Blue border on selected node. Zoom controls for image inspection. Compare button for side-by-side view. Lines connecting parent-child nodes.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>accordion</v>
+        <v>details-panel</v>
       </c>
       <c r="B11" t="str">
-        <v>Content</v>
+        <v>Interactive</v>
       </c>
       <c r="C11" t="str">
-        <v>Homepage</v>
+        <v>Inspect Page (results state - right)</v>
       </c>
       <c r="D11" t="str">
-        <v>FAQ section with heading "Still have questions?" and expandable Q&amp;A items. Questions: "Is it free?", "What is Content Credentials?", "How unique?", "What happens when I apply?", "How can it protect my content?", etc.</v>
+        <v>Right sidebar showing: filename + "Recorded by" text at top, large image preview with expand/fullscreen icon, collapsible "Content details" accordion section with subsections: "App or device used" (shows app name with icon, e.g. Adobe Content Authenticity), "Recorded by" (shows org + date, e.g. Adobe Inc. on May 4, 2026), "Actions" section listing modifications made to the content.</v>
       </c>
       <c r="E11" t="str">
-        <v>FAQ accordion (~7 questions)</v>
+        <v>Content details right panel with metadata accordion sections</v>
       </c>
       <c r="F11" t="str">
-        <v>P1 - High</v>
+        <v>P0 - Critical</v>
       </c>
       <c r="G11" t="str">
-        <v>Low</v>
+        <v>High</v>
       </c>
       <c r="H11" t="str">
-        <v>FAQ multi-open, 2-column layout (title left, items right)</v>
+        <v>Default expanded, Collapsed sections, Multiple action items</v>
       </c>
       <c r="I11" t="str">
-        <v>Left side: section title. Right side: accordion items. Clean minimal styling, border-bottom separators.</v>
+        <v>Dynamically populated from C2PA manifest data. Accordion-style collapsible sections. Shows app icons, dates, signer info with verification badges. Actions lists edits performed (crop, resize, AI-generated, etc.).</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>file-upload</v>
+        <v>compare-view</v>
       </c>
       <c r="B12" t="str">
         <v>Interactive</v>
       </c>
       <c r="C12" t="str">
-        <v>Inspect Page (empty state)</v>
+        <v>Inspect Page (compare mode)</v>
       </c>
       <c r="D12" t="str">
-        <v>Two-panel layout for the upload state. Left panel: "Inspect" heading, description text, supported formats list. Right panel: large drag-and-drop zone with dashed border, gradient icon, "Drag and drop your file" heading, "Select a file from your device" text, "Browse files" button.</v>
+        <v>Side-by-side or overlay comparison view triggered by "Compare" button in image-viewer. Shows original vs edited versions of the image for visual diff inspection.</v>
       </c>
       <c r="E12" t="str">
-        <v>File upload dropzone with info sidebar</v>
+        <v>Image comparison slider/overlay</v>
       </c>
       <c r="F12" t="str">
-        <v>P0 - Critical</v>
+        <v>P2 - Medium</v>
       </c>
       <c r="G12" t="str">
         <v>High</v>
       </c>
       <c r="H12" t="str">
-        <v>Empty state, Drag-over highlight state, Processing/loading state</v>
+        <v>Side-by-side, Overlay slider</v>
       </c>
       <c r="I12" t="str">
-        <v>Custom block with JS for drag-and-drop, file validation (AVI, AVIF, C2PA, DNG, GIF, HEIC, HEIF, JPEG, M4A, MOV, MP3, MP4, PDF, PNG, SVG, TIFF, WAV, WebP), and C2PA SDK integration.</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>credentials-panel</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Interactive</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Inspect Page (results state)</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Left sidebar showing: "Content Credentials" heading, file thumbnail with filename + recorder name (e.g. "h3-kafd-riyadh.jpg / Recorded by Adobe Inc."), "Retrieved from the selected content" note with info icon, "Search for possible matches" action link with icon, "Inspect another file or drag and drop anywhere" action link with icon.</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Content Credentials left panel with file info and actions</v>
-      </c>
-      <c r="F13" t="str">
-        <v>P0 - Critical</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Single credential, Multiple credentials (list)</v>
-      </c>
-      <c r="I13" t="str">
-        <v>Dynamically populated after file upload. Shows thumbnail preview, metadata from C2PA manifest. Action links trigger new workflows.</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>image-viewer</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Interactive</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Inspect Page (results state)</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Center panel with credential chain visualization. Shows connected image nodes in a vertical tree/flow (parent → child). Each node shows the image with a CR badge or warning icon. Includes zoom controls (+, Fit, -) and a "Compare" button.</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Credential chain viewer with zoom and compare</v>
-      </c>
-      <c r="F14" t="str">
-        <v>P0 - Critical</v>
-      </c>
-      <c r="G14" t="str">
-        <v>High</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Single node, Multi-node chain, Compare view</v>
-      </c>
-      <c r="I14" t="str">
-        <v>Complex interactive component. Displays provenance chain (history of edits). Zoom controls for image inspection. Compare button for side-by-side original vs edited. Connected nodes with lines.</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>details-panel</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Interactive</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Inspect Page (results state)</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Right sidebar showing file details: filename + recorder at top, large image preview with expand icon, collapsible "Content details" section with: "App or device used" (e.g. Adobe Content Authenticity with icon), "Recorded by" (e.g. Adobe Inc. on May 4, 2026 with icon), "Actions" section listing what was done to the content.</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Content details right panel with metadata accordion</v>
-      </c>
-      <c r="F15" t="str">
-        <v>P0 - Critical</v>
-      </c>
-      <c r="G15" t="str">
-        <v>High</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Default expanded, Collapsed sections</v>
-      </c>
-      <c r="I15" t="str">
-        <v>Dynamically populated from C2PA manifest data. Accordion-style collapsible sections. Shows app icons, dates, signer info. "Actions" lists edits (crop, resize, filter, etc.).</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>compare-view</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Interactive</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Inspect Page (compare mode)</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Side-by-side or overlay comparison view triggered by "Compare" button. Shows original vs edited versions of the image for visual diff.</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Image comparison slider/overlay</v>
-      </c>
-      <c r="F16" t="str">
-        <v>P2 - Medium</v>
-      </c>
-      <c r="G16" t="str">
-        <v>High</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Side-by-side, Overlay slider</v>
-      </c>
-      <c r="I16" t="str">
-        <v>Triggered from image-viewer "Compare" button. May use slider-based before/after pattern or toggle.</v>
+        <v>Triggered from image-viewer "Compare" button. May use slider-based before/after pattern or toggle between versions.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B42"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="100.83203125" customWidth="1"/>
@@ -799,7 +683,7 @@
         <v>Site</v>
       </c>
       <c r="B3" t="str">
-        <v>https://contentauthenticity.adobe.com</v>
+        <v>https://contentauthenticity.adobe.com/inspect</v>
       </c>
     </row>
     <row r="4">
@@ -807,7 +691,7 @@
         <v>Pages in Scope</v>
       </c>
       <c r="B4" t="str">
-        <v>Homepage, Inspect Page (empty + results state), Header, Footer</v>
+        <v>Inspect Page (empty state + results state) + Header + Footer</v>
       </c>
     </row>
     <row r="5">
@@ -815,7 +699,7 @@
         <v>Total Blocks Identified</v>
       </c>
       <c r="B5" t="str">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -836,7 +720,7 @@
         <v>P0 - Critical</v>
       </c>
       <c r="B9" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -844,7 +728,7 @@
         <v>P1 - High</v>
       </c>
       <c r="B10" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -865,7 +749,7 @@
         <v>Low</v>
       </c>
       <c r="B14" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -873,7 +757,7 @@
         <v>Medium</v>
       </c>
       <c r="B15" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -886,166 +770,145 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Page: Homepage - Blocks</v>
+        <v>Inspect Page Layout (Empty State)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>hero</v>
+        <v>Left Panel</v>
       </c>
       <c r="B19" t="str">
-        <v>Gradient hero with illustration</v>
+        <v>Heading "Inspect" + description + supported formats list</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>cards</v>
+        <v>Right Panel</v>
       </c>
       <c r="B20" t="str">
-        <v>3-up feature cards with icons</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>columns</v>
-      </c>
-      <c r="B21" t="str">
-        <v>2-col text + image (Protect your work)</v>
+        <v>Drag-and-drop file upload zone with dashed border</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>accordion</v>
-      </c>
-      <c r="B22" t="str">
-        <v>FAQ section with expandable Q&amp;A</v>
+        <v>Inspect Page Layout (Results State - 3 panels)</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Left Panel</v>
+      </c>
+      <c r="B23" t="str">
+        <v>credentials-panel: File thumbnail, name, recorder, action links</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Page: Inspect (Empty State) - Blocks</v>
+        <v>Center Panel</v>
+      </c>
+      <c r="B24" t="str">
+        <v>image-viewer: Credential chain tree, zoom controls, Compare button</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>file-upload</v>
+        <v>Right Panel</v>
       </c>
       <c r="B25" t="str">
-        <v>Info sidebar + drag-and-drop upload zone</v>
+        <v>details-panel: Image preview, Content details accordion (App, Recorder, Actions)</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Page: Inspect (Results State) - Blocks</v>
+        <v>Global Components</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>credentials-panel</v>
+        <v>Header</v>
       </c>
       <c r="B28" t="str">
-        <v>Left: file info, thumbnail, action links</v>
+        <v>Nav: Preferences, Apply, Manage, Inspect, Help | CTA: Join Discord | Profile</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>image-viewer</v>
+        <v>Footer</v>
       </c>
       <c r="B29" t="str">
-        <v>Center: credential chain tree, zoom, compare button</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>details-panel</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Right: metadata, app info, recorder, actions accordion</v>
+        <v>Minimal: legal links + copyright</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>compare-view</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Triggered overlay/side-by-side comparison</v>
+        <v>Recommended Development Phases</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Phase 1 (Foundation)</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Header, Footer, global styles/tokens, design system setup</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Recommended Development Phases</v>
+        <v>Phase 2 (Inspect Empty)</v>
+      </c>
+      <c r="B33" t="str">
+        <v>File-upload block with drag-and-drop + C2PA SDK integration</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Phase 1 (Foundation)</v>
+        <v>Phase 3 (Inspect Results)</v>
       </c>
       <c r="B34" t="str">
-        <v>Header, Footer, global styles/tokens, design system setup</v>
+        <v>Credentials-panel, Image-viewer, Details-panel</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Phase 2 (Homepage)</v>
+        <v>Phase 4 (Enhancements)</v>
       </c>
       <c r="B35" t="str">
-        <v>Hero, Cards, Columns, Accordion blocks</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Phase 3 (Inspect Core)</v>
-      </c>
-      <c r="B36" t="str">
-        <v>File-upload block with drag-and-drop + C2PA SDK integration</v>
+        <v>Compare-view, animations, error states, accessibility</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Phase 4 (Inspect Results)</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Credentials-panel, Image-viewer, Details-panel, Compare-view</v>
+        <v>Key Technical Dependencies</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>1. C2PA SDK (c2pa-js) - Required for reading Content Credentials from uploaded files</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Key Technical Notes</v>
+        <v>2. Canvas/SVG rendering - For credential chain tree visualization with connecting lines</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>1. C2PA SDK integration required for reading Content Credentials from uploaded files.</v>
+        <v>3. File API - For drag-and-drop handling and file reading</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2. Inspect results state is entirely JS-driven — blocks render dynamically based on parsed file data.</v>
+        <v>4. Image zoom/pan library - For the image viewer zoom controls</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>3. Image-viewer requires canvas/SVG for the credential chain tree visualization with connecting lines.</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>4. Details-panel uses accordion sub-sections populated from C2PA manifest (signer, actions, assertions).</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>5. Homepage blocks are standard EDS content blocks — straightforward to implement.</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>6. Header nav includes: Preferences, Apply, Manage, Inspect, Help + "Join Discord" CTA.</v>
+        <v>5. Adobe Universal Nav - For app switcher and profile integration in header</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B42"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/eds-block-mapping-report.xlsx
+++ b/eds-block-mapping-report.xlsx
@@ -4,7 +4,8 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Block Mapping" sheetId="1" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="API Flow" sheetId="2" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,17 +399,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:K12"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="36.83203125" customWidth="1"/>
     <col min="4" max="4" width="70.83203125" customWidth="1"/>
-    <col min="5" max="5" width="48.83203125" customWidth="1"/>
+    <col min="5" max="5" width="42.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="45.83203125" customWidth="1"/>
-    <col min="9" max="9" width="65.83203125" customWidth="1"/>
+    <col min="8" max="8" width="50.83203125" customWidth="1"/>
+    <col min="9" max="9" width="28.83203125" customWidth="1"/>
+    <col min="10" max="10" width="70.83203125" customWidth="1"/>
+    <col min="11" max="11" width="65.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,67 +429,49 @@
         <v>Generated: 2026-05-05</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Block Name</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Category</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Page(s)</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Description</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Original Component</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Complexity</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Variants</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Development Notes</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Excluded: Fit/Zoom controls, Compare view, Search for possible matches</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>header</v>
+        <v>Block Name</v>
       </c>
       <c r="B6" t="str">
-        <v>Navigation</v>
+        <v>Category</v>
       </c>
       <c r="C6" t="str">
-        <v>All Pages</v>
+        <v>Page(s)</v>
       </c>
       <c r="D6" t="str">
-        <v>Top navigation bar with: brand logo (Content Authenticity + Beta badge), nav links (Preferences, Apply, Manage, Inspect, Help), CTA button (Join Discord), icon button, app switcher grid, and profile/Sign in.</v>
+        <v>Description</v>
       </c>
       <c r="E6" t="str">
-        <v>Fixed top nav bar with responsive hamburger</v>
+        <v>Original Component</v>
       </c>
       <c r="F6" t="str">
-        <v>P0 - Critical</v>
+        <v>Priority</v>
       </c>
       <c r="G6" t="str">
-        <v>Medium</v>
+        <v>Complexity</v>
       </c>
       <c r="H6" t="str">
-        <v>Desktop (full nav links), Mobile (hamburger + slide-out)</v>
+        <v>Variants</v>
       </c>
       <c r="I6" t="str">
-        <v>Nav links: Preferences, Apply, Manage, Inspect, Help. CTA: "Join Discord". Uses Adobe Universal Nav for app switcher + profile. Sticky positioned.</v>
+        <v>API Responsibility</v>
+      </c>
+      <c r="J6" t="str">
+        <v>API Data Flow</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Development Notes</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>footer</v>
+        <v>header</v>
       </c>
       <c r="B7" t="str">
         <v>Navigation</v>
@@ -495,126 +480,150 @@
         <v>All Pages</v>
       </c>
       <c r="D7" t="str">
-        <v>Minimal footer with Adobe branding, legal links, and copyright notice.</v>
+        <v>Top navigation bar with: brand logo (Content Authenticity + Beta badge), nav links (Preferences, Apply, Manage, Inspect, Help), CTA button (Join Discord), icon button, app switcher grid, and profile/Sign in.</v>
       </c>
       <c r="E7" t="str">
-        <v>Minimal site footer</v>
+        <v>Fixed top nav bar with responsive hamburger</v>
       </c>
       <c r="F7" t="str">
-        <v>P1 - High</v>
+        <v>P0 - Critical</v>
       </c>
       <c r="G7" t="str">
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="H7" t="str">
-        <v>Minimal (links + copyright)</v>
+        <v>Desktop (full nav links), Mobile (hamburger + slide-out)</v>
       </c>
       <c r="I7" t="str">
-        <v>Lightweight footer following Adobe standard pattern.</v>
+        <v>N/A</v>
+      </c>
+      <c r="J7" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Nav links: Preferences, Apply, Manage, Inspect, Help. CTA: "Join Discord". Uses Adobe Universal Nav for app switcher + profile. Sticky positioned.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>file-upload</v>
+        <v>footer</v>
       </c>
       <c r="B8" t="str">
-        <v>Interactive</v>
+        <v>Navigation</v>
       </c>
       <c r="C8" t="str">
-        <v>Inspect Page (empty state)</v>
+        <v>All Pages</v>
       </c>
       <c r="D8" t="str">
-        <v>Two-panel layout for the upload state. Left panel: "Inspect" heading, description text, supported formats list (AVI, AVIF, C2PA, DNG, GIF, HEIC, HEIF, JPEG, M4A, MOV, MP3, MP4, PDF, PNG, SVG, TIFF, WAV, WebP). Right panel: large drag-and-drop zone with rounded dashed border, gradient icon (image + checkmark), "Drag and drop your file" heading, "Select a file from your device" text, "Browse files" button.</v>
+        <v>Minimal footer with Adobe branding, legal links, and copyright notice.</v>
       </c>
       <c r="E8" t="str">
-        <v>File upload dropzone with info sidebar</v>
+        <v>Minimal site footer</v>
       </c>
       <c r="F8" t="str">
-        <v>P0 - Critical</v>
+        <v>P1 - High</v>
       </c>
       <c r="G8" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="H8" t="str">
-        <v>Empty state, Drag-over highlight state, Processing/loading state</v>
+        <v>Minimal (links + copyright)</v>
       </c>
       <c r="I8" t="str">
-        <v>Custom block with JS for drag-and-drop, file validation, and C2PA SDK integration. Supported formats list displayed in left panel.</v>
+        <v>N/A</v>
+      </c>
+      <c r="J8" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Lightweight footer following Adobe standard pattern.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>credentials-panel</v>
+        <v>file-upload</v>
       </c>
       <c r="B9" t="str">
         <v>Interactive</v>
       </c>
       <c r="C9" t="str">
-        <v>Inspect Page (results state - left)</v>
+        <v>Inspect Page (empty state + API orchestrator)</v>
       </c>
       <c r="D9" t="str">
-        <v>Left sidebar showing: "Content Credentials" heading, file thumbnail with filename + recorder name (e.g. "h3-kafd-riyadh.jpg / Recorded by Adobe Inc."), "Retrieved from the selected content" note with info icon, "Search for possible matches" action link with search icon, "Inspect another file or drag and drop anywhere" action link with upload icon.</v>
+        <v>Two-panel layout for the upload state. Left panel: "Inspect" heading, description text, supported formats list. Right panel: drag-and-drop zone with dashed border, gradient icon, "Drag and drop your file" heading, "Browse files" button. THIS BLOCK ALSO HANDLES THE API CALL: after file is uploaded, it calls the Content Credentials API to retrieve image details, then renders the results state by populating credentials-panel, image-viewer, and details-panel with the response data.</v>
       </c>
       <c r="E9" t="str">
-        <v>Content Credentials left panel with file info and actions</v>
+        <v>File upload dropzone + API orchestrator</v>
       </c>
       <c r="F9" t="str">
         <v>P0 - Critical</v>
       </c>
       <c r="G9" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="H9" t="str">
-        <v>Single credential, Multiple credentials (list)</v>
+        <v>Empty state (upload UI), Drag-over highlight, Loading/processing, Results state (3-panel view)</v>
       </c>
       <c r="I9" t="str">
-        <v>Dynamically populated after file upload. Shows thumbnail preview, metadata from C2PA manifest. Action links trigger new workflows. Fixed-width sidebar.</v>
+        <v>YES — Primary API handler</v>
+      </c>
+      <c r="J9" t="str">
+        <v>1. User uploads/drops file → 2. file-upload block sends file to Content Credentials API → 3. API returns credential details (manifest, chain, actions, ingredients) → 4. Block transitions from empty state to results state → 5. Populates credentials-panel, image-viewer, and details-panel with parsed API response</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Single orchestrator block. Handles file input, API call, loading state, error handling, and data distribution to child panels. On "Inspect another file" click, resets back to empty state.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>image-viewer</v>
+        <v>credentials-panel</v>
       </c>
       <c r="B10" t="str">
         <v>Interactive</v>
       </c>
       <c r="C10" t="str">
-        <v>Inspect Page (results state - center)</v>
+        <v>Inspect Page (results state - left)</v>
       </c>
       <c r="D10" t="str">
-        <v>Center panel with credential chain visualization. Shows connected image nodes in a vertical tree/flow (parent → child with connecting lines). Each node shows the image with a CR badge (valid) or warning triangle icon (issue). Includes zoom controls (+, Fit, -) and a "Compare" button at bottom.</v>
+        <v>Left sidebar showing: "Content Credentials" heading, file thumbnail with filename + recorder name (e.g. "h3-kafd-riyadh.jpg / Recorded by Adobe Inc."), "Retrieved from the selected content" note with info icon, "Inspect another file or drag and drop anywhere" action link with upload icon.</v>
       </c>
       <c r="E10" t="str">
-        <v>Credential chain viewer with zoom and compare</v>
+        <v>Content Credentials left panel with file info and actions</v>
       </c>
       <c r="F10" t="str">
         <v>P0 - Critical</v>
       </c>
       <c r="G10" t="str">
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="H10" t="str">
-        <v>Single node, Multi-node chain (vertical tree), Compare mode</v>
+        <v>Single credential, Multiple credentials (list)</v>
       </c>
       <c r="I10" t="str">
-        <v>Complex interactive component. Displays provenance chain (history of edits). Blue border on selected node. Zoom controls for image inspection. Compare button for side-by-side view. Lines connecting parent-child nodes.</v>
+        <v>NO — Receives data from file-upload block</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Populated by file-upload block with: filename, thumbnail, recorder/signer name from API response</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Rendered by file-upload block after API success. Shows thumbnail preview, metadata from API response. "Inspect another file" resets the file-upload block to empty state.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>details-panel</v>
+        <v>image-viewer</v>
       </c>
       <c r="B11" t="str">
         <v>Interactive</v>
       </c>
       <c r="C11" t="str">
-        <v>Inspect Page (results state - right)</v>
+        <v>Inspect Page (results state - center)</v>
       </c>
       <c r="D11" t="str">
-        <v>Right sidebar showing: filename + "Recorded by" text at top, large image preview with expand/fullscreen icon, collapsible "Content details" accordion section with subsections: "App or device used" (shows app name with icon, e.g. Adobe Content Authenticity), "Recorded by" (shows org + date, e.g. Adobe Inc. on May 4, 2026), "Actions" section listing modifications made to the content.</v>
+        <v>Center panel with credential chain visualization. Shows connected image nodes in a vertical tree/flow (parent → child with connecting lines). Top node shows uploaded image with CR badge. Child nodes show ingredient/source images with warning triangle if invalid. Blue border on selected node.</v>
       </c>
       <c r="E11" t="str">
-        <v>Content details right panel with metadata accordion sections</v>
+        <v>Credential chain tree viewer</v>
       </c>
       <c r="F11" t="str">
         <v>P0 - Critical</v>
@@ -623,53 +632,275 @@
         <v>High</v>
       </c>
       <c r="H11" t="str">
-        <v>Default expanded, Collapsed sections, Multiple action items</v>
+        <v>Single node, Multi-node chain (vertical tree)</v>
       </c>
       <c r="I11" t="str">
-        <v>Dynamically populated from C2PA manifest data. Accordion-style collapsible sections. Shows app icons, dates, signer info with verification badges. Actions lists edits performed (crop, resize, AI-generated, etc.).</v>
+        <v>NO — Receives data from file-upload block</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Populated by file-upload block with: credential chain/manifest data (parent-child relationships, images, validity status) from API response</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Rendered by file-upload block after API success. Displays provenance chain. Blue border highlights selected node. Clicking a node updates the details-panel with that node's specific details.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>compare-view</v>
+        <v>details-panel</v>
       </c>
       <c r="B12" t="str">
         <v>Interactive</v>
       </c>
       <c r="C12" t="str">
-        <v>Inspect Page (compare mode)</v>
+        <v>Inspect Page (results state - right)</v>
       </c>
       <c r="D12" t="str">
-        <v>Side-by-side or overlay comparison view triggered by "Compare" button in image-viewer. Shows original vs edited versions of the image for visual diff inspection.</v>
+        <v>Right sidebar showing: filename + "Recorded by" at top, then scrollable sections — "Content details" (info about content and how it was made), "App or device used" (e.g. Adobe Content Authenticity with icon), "Recorded by" (e.g. Adobe Inc. on May 4, 2026), "Actions" (e.g. "Opened - Opened a pre-existing file", "Watermarked - Applied an invisible watermark..."), "Ingredients" (source assets with thumbnail + label + validity).</v>
       </c>
       <c r="E12" t="str">
-        <v>Image comparison slider/overlay</v>
+        <v>Content details right panel with metadata sections</v>
       </c>
       <c r="F12" t="str">
-        <v>P2 - Medium</v>
+        <v>P0 - Critical</v>
       </c>
       <c r="G12" t="str">
         <v>High</v>
       </c>
       <c r="H12" t="str">
-        <v>Side-by-side, Overlay slider</v>
+        <v>Full details view, Collapsed sections</v>
       </c>
       <c r="I12" t="str">
-        <v>Triggered from image-viewer "Compare" button. May use slider-based before/after pattern or toggle between versions.</v>
+        <v>NO — Receives data from file-upload block</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Populated by file-upload block with: detailed metadata from API response (app info, signer, actions list, ingredients list). Updates when user clicks different nodes in image-viewer.</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Rendered by file-upload block after API success. Sections: Content details, App/device, Recorded by, Actions, Ingredients. Updates dynamically when user selects different credential chain nodes.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:D20"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="80.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>API Integration Flow - file-upload block</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>The file-upload block is the single orchestrator for API calls and data distribution.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Step</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Action</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Block</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Details</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>User drops/selects file</v>
+      </c>
+      <c r="C6" t="str">
+        <v>file-upload</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Validates file type against supported formats list</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Show loading state</v>
+      </c>
+      <c r="C7" t="str">
+        <v>file-upload</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Displays processing indicator while API call is in progress</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>3</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Call Content Credentials API</v>
+      </c>
+      <c r="C8" t="str">
+        <v>file-upload</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Sends file to API endpoint, receives credential manifest data</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>4</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Parse API response</v>
+      </c>
+      <c r="C9" t="str">
+        <v>file-upload</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Extracts: chain data, metadata, actions, ingredients, signer info</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Transition to results state</v>
+      </c>
+      <c r="C10" t="str">
+        <v>file-upload</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Hides upload UI, renders 3-panel results layout</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>6</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Populate credentials-panel</v>
+      </c>
+      <c r="C11" t="str">
+        <v>credentials-panel</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Receives: filename, thumbnail, recorder name</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>7</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Populate image-viewer</v>
+      </c>
+      <c r="C12" t="str">
+        <v>image-viewer</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Receives: credential chain nodes, parent-child relationships, validity status</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>8</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Populate details-panel</v>
+      </c>
+      <c r="C13" t="str">
+        <v>details-panel</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Receives: app info, signer, date, actions list, ingredients list</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>9</v>
+      </c>
+      <c r="B14" t="str">
+        <v>User clicks chain node</v>
+      </c>
+      <c r="C14" t="str">
+        <v>image-viewer → details-panel</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Selected node updates details-panel with that node's specific metadata</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>10</v>
+      </c>
+      <c r="B15" t="str">
+        <v>User clicks "Inspect another file"</v>
+      </c>
+      <c r="C15" t="str">
+        <v>credentials-panel → file-upload</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Resets file-upload block back to empty/upload state</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Error Handling</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>API failure</v>
+      </c>
+      <c r="B18" t="str">
+        <v>file-upload shows error message with retry option</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Invalid file type</v>
+      </c>
+      <c r="B19" t="str">
+        <v>file-upload shows inline validation error before API call</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>No credentials found</v>
+      </c>
+      <c r="B20" t="str">
+        <v>file-upload shows "No Content Credentials found" message with guidance</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D20"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B34"/>
+  <cols>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="100.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -699,7 +930,7 @@
         <v>Total Blocks Identified</v>
       </c>
       <c r="B5" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -710,205 +941,178 @@
         <v>SvelteKit + Adobe Spectrum Design System (Tailwind CSS)</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Excluded Features</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Fit/Zoom controls, Compare view, Search for possible matches</v>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Priority Breakdown</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>P0 - Critical</v>
-      </c>
-      <c r="B9" t="str">
-        <v>5</v>
+        <v>API Handler Block</v>
+      </c>
+      <c r="B8" t="str">
+        <v>file-upload (single orchestrator for all API calls)</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>P1 - High</v>
-      </c>
-      <c r="B10" t="str">
-        <v>1</v>
+        <v>Priority Breakdown</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>P2 - Medium</v>
+        <v>P0 - Critical</v>
       </c>
       <c r="B11" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>P1 - High</v>
+      </c>
+      <c r="B12" t="str">
         <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Complexity Breakdown</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Low</v>
-      </c>
-      <c r="B14" t="str">
-        <v>1</v>
+        <v>Inspect Page Layout (Empty State)</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Medium</v>
+        <v>Left Panel</v>
       </c>
       <c r="B15" t="str">
-        <v>2</v>
+        <v>"Inspect" heading + description + supported formats list</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>High</v>
+        <v>Right Panel</v>
       </c>
       <c r="B16" t="str">
-        <v>4</v>
+        <v>Drag-and-drop file upload zone + Browse files button</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Inspect Page Layout (Empty State)</v>
+        <v>Inspect Page Layout (Results State - 3 panels)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Left Panel</v>
+        <v>Left Panel (credentials-panel)</v>
       </c>
       <c r="B19" t="str">
-        <v>Heading "Inspect" + description + supported formats list</v>
+        <v>Content Credentials heading, thumbnail + name + recorder, "Inspect another file" link</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Right Panel</v>
+        <v>Center Panel (image-viewer)</v>
       </c>
       <c r="B20" t="str">
-        <v>Drag-and-drop file upload zone with dashed border</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Inspect Page Layout (Results State - 3 panels)</v>
+        <v>Credential chain tree: parent image (CR badge) → child nodes (warning if invalid)</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Right Panel (details-panel)</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Content details, App used, Recorded by, Actions (Opened, Watermarked), Ingredients</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Left Panel</v>
-      </c>
-      <c r="B23" t="str">
-        <v>credentials-panel: File thumbnail, name, recorder, action links</v>
+        <v>API Architecture</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Center Panel</v>
+        <v>Orchestrator</v>
       </c>
       <c r="B24" t="str">
-        <v>image-viewer: Credential chain tree, zoom controls, Compare button</v>
+        <v>file-upload block handles all API communication</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Right Panel</v>
+        <v>Data flow</v>
       </c>
       <c r="B25" t="str">
-        <v>details-panel: Image preview, Content details accordion (App, Recorder, Actions)</v>
+        <v>file-upload → calls API → distributes response to 3 result panels</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>State management</v>
+      </c>
+      <c r="B26" t="str">
+        <v>file-upload manages empty state ↔ results state transitions</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Global Components</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Header</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Nav: Preferences, Apply, Manage, Inspect, Help | CTA: Join Discord | Profile</v>
+        <v>Inter-block comms</v>
+      </c>
+      <c r="B27" t="str">
+        <v>image-viewer node click → updates details-panel content</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Footer</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Minimal: legal links + copyright</v>
+        <v>Recommended Development Phases</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Phase 1 (Foundation)</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Header, Footer, global styles/tokens, design system setup</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Recommended Development Phases</v>
+        <v>Phase 2 (Inspect Empty)</v>
+      </c>
+      <c r="B31" t="str">
+        <v>file-upload block: upload UI, drag-and-drop, file validation</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Phase 1 (Foundation)</v>
+        <v>Phase 3 (API Integration)</v>
       </c>
       <c r="B32" t="str">
-        <v>Header, Footer, global styles/tokens, design system setup</v>
+        <v>file-upload block: API call, loading state, error handling, state transition</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Phase 2 (Inspect Empty)</v>
+        <v>Phase 4 (Results Panels)</v>
       </c>
       <c r="B33" t="str">
-        <v>File-upload block with drag-and-drop + C2PA SDK integration</v>
+        <v>credentials-panel, image-viewer (chain tree), details-panel rendering</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Phase 3 (Inspect Results)</v>
+        <v>Phase 5 (Interactions)</v>
       </c>
       <c r="B34" t="str">
-        <v>Credentials-panel, Image-viewer, Details-panel</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Phase 4 (Enhancements)</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Compare-view, animations, error states, accessibility</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Key Technical Dependencies</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>1. C2PA SDK (c2pa-js) - Required for reading Content Credentials from uploaded files</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>2. Canvas/SVG rendering - For credential chain tree visualization with connecting lines</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>3. File API - For drag-and-drop handling and file reading</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>4. Image zoom/pan library - For the image viewer zoom controls</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>5. Adobe Universal Nav - For app switcher and profile integration in header</v>
+        <v>Node selection updates details, "Inspect another file" reset flow</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B34"/>
   </ignoredErrors>
 </worksheet>
 </file>